--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/OHIO_2017.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/OHIO_2017.xlsx
@@ -481,7 +481,7 @@
         <v>5</v>
       </c>
       <c r="D7">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="8">
@@ -535,7 +535,7 @@
         <v>5</v>
       </c>
       <c r="D10">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="11">
@@ -1147,7 +1147,7 @@
         <v>5</v>
       </c>
       <c r="D44">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="45">
@@ -1237,7 +1237,7 @@
         <v>5</v>
       </c>
       <c r="D49">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="50">
@@ -1363,7 +1363,7 @@
         <v>5</v>
       </c>
       <c r="D56">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="57">
@@ -1489,7 +1489,7 @@
         <v>5</v>
       </c>
       <c r="D63">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="64">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C87">
@@ -2263,7 +2263,7 @@
         <v>5</v>
       </c>
       <c r="D106">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="107">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C123">
@@ -2587,7 +2587,7 @@
         <v>5</v>
       </c>
       <c r="D124">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="125">
@@ -2839,7 +2839,7 @@
         <v>5</v>
       </c>
       <c r="D138">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="139">
@@ -3037,7 +3037,7 @@
         <v>5</v>
       </c>
       <c r="D149">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="150">
@@ -3235,7 +3235,7 @@
         <v>5</v>
       </c>
       <c r="D160">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="161">
@@ -3451,7 +3451,7 @@
         <v>5</v>
       </c>
       <c r="D172">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="173">
@@ -3631,7 +3631,7 @@
         <v>5</v>
       </c>
       <c r="D182">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="183">
@@ -3703,7 +3703,7 @@
         <v>49</v>
       </c>
       <c r="D186">
-        <v>0.009492444788841535</v>
+        <v>0.009492444788841536</v>
       </c>
     </row>
     <row r="187">
@@ -3739,7 +3739,7 @@
         <v>5</v>
       </c>
       <c r="D188">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="189">
@@ -3811,7 +3811,7 @@
         <v>5</v>
       </c>
       <c r="D192">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="193">
@@ -4200,14 +4200,14 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C214">
         <v>5</v>
       </c>
       <c r="D214">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="215">
@@ -4855,7 +4855,7 @@
         <v>5</v>
       </c>
       <c r="D250">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="251">
@@ -5089,7 +5089,7 @@
         <v>5</v>
       </c>
       <c r="D263">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="264">
@@ -5701,7 +5701,7 @@
         <v>5</v>
       </c>
       <c r="D297">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="298">
@@ -6169,7 +6169,7 @@
         <v>5</v>
       </c>
       <c r="D323">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="324">
@@ -6331,7 +6331,7 @@
         <v>5</v>
       </c>
       <c r="D332">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="333">
@@ -6583,7 +6583,7 @@
         <v>5</v>
       </c>
       <c r="D346">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="347">
@@ -6745,7 +6745,7 @@
         <v>5</v>
       </c>
       <c r="D355">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="356">
@@ -7123,7 +7123,7 @@
         <v>5</v>
       </c>
       <c r="D376">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="377">
@@ -7663,7 +7663,7 @@
         <v>5</v>
       </c>
       <c r="D406">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="407">
@@ -7771,7 +7771,7 @@
         <v>5</v>
       </c>
       <c r="D412">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="413">
@@ -8257,7 +8257,7 @@
         <v>5</v>
       </c>
       <c r="D439">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="440">
@@ -8725,7 +8725,7 @@
         <v>5</v>
       </c>
       <c r="D465">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="466">
@@ -9265,7 +9265,7 @@
         <v>5</v>
       </c>
       <c r="D495">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="496">
@@ -9283,7 +9283,7 @@
         <v>5</v>
       </c>
       <c r="D496">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="497">
@@ -9337,7 +9337,7 @@
         <v>5</v>
       </c>
       <c r="D499">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="500">
@@ -9427,7 +9427,7 @@
         <v>5</v>
       </c>
       <c r="D504">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="505">
@@ -9661,7 +9661,7 @@
         <v>5</v>
       </c>
       <c r="D517">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="518">
@@ -10194,7 +10194,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C547">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C548">
@@ -10255,7 +10255,7 @@
         <v>5</v>
       </c>
       <c r="D550">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="551">
@@ -10752,7 +10752,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C578">
@@ -10770,7 +10770,7 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C579">
@@ -10813,7 +10813,7 @@
         <v>5</v>
       </c>
       <c r="D581">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="582">
@@ -10975,7 +10975,7 @@
         <v>5</v>
       </c>
       <c r="D590">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="591">
@@ -11119,7 +11119,7 @@
         <v>5</v>
       </c>
       <c r="D598">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="599">
@@ -11965,7 +11965,7 @@
         <v>5</v>
       </c>
       <c r="D645">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="646">
@@ -12055,7 +12055,7 @@
         <v>5</v>
       </c>
       <c r="D650">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="651">
@@ -12163,7 +12163,7 @@
         <v>49</v>
       </c>
       <c r="D656">
-        <v>0.009492444788841535</v>
+        <v>0.009492444788841536</v>
       </c>
     </row>
     <row r="657">
@@ -12361,7 +12361,7 @@
         <v>5</v>
       </c>
       <c r="D667">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="668">
@@ -13567,7 +13567,7 @@
         <v>5</v>
       </c>
       <c r="D734">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="735">
@@ -13639,7 +13639,7 @@
         <v>5</v>
       </c>
       <c r="D738">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="739">
@@ -13819,7 +13819,7 @@
         <v>5</v>
       </c>
       <c r="D748">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="749">
@@ -13873,7 +13873,7 @@
         <v>5</v>
       </c>
       <c r="D751">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="752">
@@ -14251,7 +14251,7 @@
         <v>5</v>
       </c>
       <c r="D772">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="773">
@@ -14539,7 +14539,7 @@
         <v>5</v>
       </c>
       <c r="D788">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="789">
@@ -14629,7 +14629,7 @@
         <v>5</v>
       </c>
       <c r="D793">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="794">
@@ -14755,7 +14755,7 @@
         <v>5</v>
       </c>
       <c r="D800">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="801">
@@ -14917,7 +14917,7 @@
         <v>5</v>
       </c>
       <c r="D809">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="810">
@@ -15511,7 +15511,7 @@
         <v>5</v>
       </c>
       <c r="D842">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="843">
@@ -16141,7 +16141,7 @@
         <v>5</v>
       </c>
       <c r="D877">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="878">
@@ -16213,7 +16213,7 @@
         <v>5</v>
       </c>
       <c r="D881">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="882">
@@ -16447,7 +16447,7 @@
         <v>5</v>
       </c>
       <c r="D894">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="895">
@@ -16609,7 +16609,7 @@
         <v>5</v>
       </c>
       <c r="D903">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="904">
@@ -17077,7 +17077,7 @@
         <v>5</v>
       </c>
       <c r="D929">
-        <v>0.0009686168151879117</v>
+        <v>0.0009686168151879116</v>
       </c>
     </row>
     <row r="930">
